--- a/dataset/participation_sample.xlsx
+++ b/dataset/participation_sample.xlsx
@@ -1,37 +1,156 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2E7B82-1F17-4598-A94E-D8CB481E2E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="4380" yWindow="2625" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t>성명</t>
+  </si>
+  <si>
+    <t>참여 (1)</t>
+  </si>
+  <si>
+    <t>강경원</t>
+  </si>
+  <si>
+    <t>김신정</t>
+  </si>
+  <si>
+    <t>김재혁</t>
+  </si>
+  <si>
+    <t>김재현</t>
+  </si>
+  <si>
+    <t>김종욱</t>
+  </si>
+  <si>
+    <t>문민영</t>
+  </si>
+  <si>
+    <t>문정현</t>
+  </si>
+  <si>
+    <t>박창민</t>
+  </si>
+  <si>
+    <t>서윤식</t>
+  </si>
+  <si>
+    <t>서지영</t>
+  </si>
+  <si>
+    <t>안재현</t>
+  </si>
+  <si>
+    <t>이도훈</t>
+  </si>
+  <si>
+    <t>이영준</t>
+  </si>
+  <si>
+    <t>이영호</t>
+  </si>
+  <si>
+    <t>이찬호</t>
+  </si>
+  <si>
+    <t>이희연</t>
+  </si>
+  <si>
+    <t>정우용</t>
+  </si>
+  <si>
+    <t>정준섭</t>
+  </si>
+  <si>
+    <t>정지윤</t>
+  </si>
+  <si>
+    <t>정혜린</t>
+  </si>
+  <si>
+    <t>최지원</t>
+  </si>
+  <si>
+    <t>카밀라</t>
+  </si>
+  <si>
+    <t>한지윤</t>
+  </si>
+  <si>
+    <t>남1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +165,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,219 +489,165 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>성명</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>참여 (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>강경원</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>김신정</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>김재혁</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>김재현</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>김종욱</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>문민영</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>문정현</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>박창민</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>서윤식</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>서지영</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>안재현</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>이도훈</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>이영준</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>이영호</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>이찬호</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>이희연</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>정우용</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>정준섭</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>정지윤</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>정혜린</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>최지원</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>카밀라</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>한종호</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>한지윤</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dataset/participation_sample.xlsx
+++ b/dataset/participation_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2E7B82-1F17-4598-A94E-D8CB481E2E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2092F554-78B3-41DA-B280-E031A58EE95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="2625" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -97,28 +97,23 @@
     <t>한지윤</t>
   </si>
   <si>
-    <t>남1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>남2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>남3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>여1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>여2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>여3</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김양우</t>
+  </si>
+  <si>
+    <t>양현철</t>
+  </si>
+  <si>
+    <t>박종운</t>
+  </si>
+  <si>
+    <t>종운동생</t>
+  </si>
+  <si>
+    <t>민규</t>
   </si>
 </sst>
 </file>
@@ -618,32 +613,32 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/participation_sample.xlsx
+++ b/dataset/participation_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2092F554-78B3-41DA-B280-E031A58EE95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE55D42B-4DD4-430A-B854-9AFA7FB69274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1185" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>성명</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>정혜린</t>
-  </si>
-  <si>
-    <t>최지원</t>
   </si>
   <si>
     <t>카밀라</t>
@@ -101,19 +98,24 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>김양우</t>
-  </si>
-  <si>
-    <t>양현철</t>
-  </si>
-  <si>
-    <t>박종운</t>
-  </si>
-  <si>
-    <t>종운동생</t>
-  </si>
-  <si>
-    <t>민규</t>
+    <t>남1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -485,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -498,72 +500,72 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -578,37 +580,37 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
@@ -633,12 +635,7 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/participation_sample.xlsx
+++ b/dataset/participation_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE55D42B-4DD4-430A-B854-9AFA7FB69274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749ED8DF-D709-4EDD-912F-8B09F6DCEB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1185" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="1185" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -500,72 +500,72 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -580,32 +580,32 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">

--- a/dataset/participation_sample.xlsx
+++ b/dataset/participation_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749ED8DF-D709-4EDD-912F-8B09F6DCEB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B325B5-2ED4-4D84-8530-350EB91963A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1185" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4845" yWindow="465" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -88,9 +88,6 @@
     <t>정혜린</t>
   </si>
   <si>
-    <t>카밀라</t>
-  </si>
-  <si>
     <t>한지윤</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
   <si>
     <t>여2</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>까밀라</t>
   </si>
 </sst>
 </file>
@@ -600,42 +600,42 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/participation_sample.xlsx
+++ b/dataset/participation_sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B325B5-2ED4-4D84-8530-350EB91963A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBE5D3E-660F-40C5-A982-E9D4C1DA8E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4845" yWindow="465" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>성명</t>
   </si>
@@ -91,31 +91,43 @@
     <t>한지윤</t>
   </si>
   <si>
-    <t>여3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>남1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>남2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>남3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>여1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>여2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>까밀라</t>
+  </si>
+  <si>
+    <t>남1.1</t>
+  </si>
+  <si>
+    <t>남1.2</t>
+  </si>
+  <si>
+    <t>남2.1</t>
+  </si>
+  <si>
+    <t>남2.2</t>
+  </si>
+  <si>
+    <t>남3.1</t>
+  </si>
+  <si>
+    <t>남3.2</t>
+  </si>
+  <si>
+    <t>여1.1</t>
+  </si>
+  <si>
+    <t>여1.2</t>
+  </si>
+  <si>
+    <t>여2.1</t>
+  </si>
+  <si>
+    <t>여2.2</t>
+  </si>
+  <si>
+    <t>여3.1</t>
+  </si>
+  <si>
+    <t>여3.2</t>
   </si>
 </sst>
 </file>
@@ -487,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -600,7 +612,7 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
@@ -635,7 +647,37 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/participation_sample.xlsx
+++ b/dataset/participation_sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBE5D3E-660F-40C5-A982-E9D4C1DA8E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D165EE1-28A4-441F-AEFA-24919A842D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="1185" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,40 +94,41 @@
     <t>까밀라</t>
   </si>
   <si>
-    <t>남1.1</t>
-  </si>
-  <si>
     <t>남1.2</t>
   </si>
   <si>
-    <t>남2.1</t>
-  </si>
-  <si>
-    <t>남2.2</t>
-  </si>
-  <si>
     <t>남3.1</t>
   </si>
   <si>
     <t>남3.2</t>
   </si>
   <si>
-    <t>여1.1</t>
-  </si>
-  <si>
     <t>여1.2</t>
   </si>
   <si>
-    <t>여2.1</t>
-  </si>
-  <si>
     <t>여2.2</t>
   </si>
   <si>
-    <t>여3.1</t>
-  </si>
-  <si>
     <t>여3.2</t>
+  </si>
+  <si>
+    <t>이휘영</t>
+  </si>
+  <si>
+    <t>까미게스트</t>
+  </si>
+  <si>
+    <t>수현남편님</t>
+  </si>
+  <si>
+    <t>박수현</t>
+  </si>
+  <si>
+    <t>최지원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김예진</t>
   </si>
 </sst>
 </file>
@@ -622,62 +623,62 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/participation_sample.xlsx
+++ b/dataset/participation_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D165EE1-28A4-441F-AEFA-24919A842D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CEFD9C-3DB3-4786-BE95-209EBD736573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1185" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15550" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>성명</t>
   </si>
@@ -92,43 +92,6 @@
   </si>
   <si>
     <t>까밀라</t>
-  </si>
-  <si>
-    <t>남1.2</t>
-  </si>
-  <si>
-    <t>남3.1</t>
-  </si>
-  <si>
-    <t>남3.2</t>
-  </si>
-  <si>
-    <t>여1.2</t>
-  </si>
-  <si>
-    <t>여2.2</t>
-  </si>
-  <si>
-    <t>여3.2</t>
-  </si>
-  <si>
-    <t>이휘영</t>
-  </si>
-  <si>
-    <t>까미게스트</t>
-  </si>
-  <si>
-    <t>수현남편님</t>
-  </si>
-  <si>
-    <t>박수현</t>
-  </si>
-  <si>
-    <t>최지원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김예진</t>
   </si>
 </sst>
 </file>
@@ -500,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -621,66 +584,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>29</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
